--- a/artfynd/A 13529-2026 artfynd.xlsx
+++ b/artfynd/A 13529-2026 artfynd.xlsx
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132706120</v>
+        <v>132706133</v>
       </c>
       <c r="B8" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485504</v>
+        <v>485379</v>
       </c>
       <c r="R8" t="n">
-        <v>7085265</v>
+        <v>7085196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132706133</v>
+        <v>132706120</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485379</v>
+        <v>485504</v>
       </c>
       <c r="R9" t="n">
-        <v>7085196</v>
+        <v>7085265</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132706118</v>
+        <v>132706130</v>
       </c>
       <c r="B12" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485671</v>
+        <v>485688</v>
       </c>
       <c r="R12" t="n">
-        <v>7085660</v>
+        <v>7085710</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1736,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,10 +1767,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132706130</v>
+        <v>132706118</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1778,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485688</v>
+        <v>485671</v>
       </c>
       <c r="R13" t="n">
-        <v>7085710</v>
+        <v>7085660</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1833,11 +1838,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 13529-2026 artfynd.xlsx
+++ b/artfynd/A 13529-2026 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132706119</v>
+        <v>132706122</v>
       </c>
       <c r="B4" t="n">
-        <v>80438</v>
+        <v>91914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485670</v>
+        <v>485491</v>
       </c>
       <c r="R4" t="n">
-        <v>7085635</v>
+        <v>7085550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132706122</v>
+        <v>132706119</v>
       </c>
       <c r="B5" t="n">
-        <v>91914</v>
+        <v>80438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485491</v>
+        <v>485670</v>
       </c>
       <c r="R5" t="n">
-        <v>7085550</v>
+        <v>7085635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132706129</v>
+        <v>132706117</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485559</v>
+        <v>485449</v>
       </c>
       <c r="R6" t="n">
-        <v>7085853</v>
+        <v>7085557</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132706117</v>
+        <v>132706129</v>
       </c>
       <c r="B7" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485449</v>
+        <v>485559</v>
       </c>
       <c r="R7" t="n">
-        <v>7085557</v>
+        <v>7085853</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132706133</v>
+        <v>132706120</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485379</v>
+        <v>485504</v>
       </c>
       <c r="R8" t="n">
-        <v>7085196</v>
+        <v>7085265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132706120</v>
+        <v>132706133</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485504</v>
+        <v>485379</v>
       </c>
       <c r="R9" t="n">
-        <v>7085265</v>
+        <v>7085196</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132706130</v>
+        <v>132706118</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485688</v>
+        <v>485671</v>
       </c>
       <c r="R12" t="n">
-        <v>7085710</v>
+        <v>7085660</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132706118</v>
+        <v>132706130</v>
       </c>
       <c r="B13" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485671</v>
+        <v>485688</v>
       </c>
       <c r="R13" t="n">
-        <v>7085660</v>
+        <v>7085710</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,6 +1833,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 13529-2026 artfynd.xlsx
+++ b/artfynd/A 13529-2026 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132706122</v>
+        <v>132706119</v>
       </c>
       <c r="B4" t="n">
-        <v>91914</v>
+        <v>80438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485491</v>
+        <v>485670</v>
       </c>
       <c r="R4" t="n">
-        <v>7085550</v>
+        <v>7085635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132706119</v>
+        <v>132706122</v>
       </c>
       <c r="B5" t="n">
-        <v>80438</v>
+        <v>91914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485670</v>
+        <v>485491</v>
       </c>
       <c r="R5" t="n">
-        <v>7085635</v>
+        <v>7085550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132706120</v>
+        <v>132706133</v>
       </c>
       <c r="B8" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485504</v>
+        <v>485379</v>
       </c>
       <c r="R8" t="n">
-        <v>7085265</v>
+        <v>7085196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132706133</v>
+        <v>132706120</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485379</v>
+        <v>485504</v>
       </c>
       <c r="R9" t="n">
-        <v>7085196</v>
+        <v>7085265</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132706118</v>
+        <v>132706130</v>
       </c>
       <c r="B12" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485671</v>
+        <v>485688</v>
       </c>
       <c r="R12" t="n">
-        <v>7085660</v>
+        <v>7085710</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1736,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,10 +1767,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132706130</v>
+        <v>132706118</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1778,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485688</v>
+        <v>485671</v>
       </c>
       <c r="R13" t="n">
-        <v>7085710</v>
+        <v>7085660</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1833,11 +1838,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 13529-2026 artfynd.xlsx
+++ b/artfynd/A 13529-2026 artfynd.xlsx
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132706133</v>
+        <v>132706120</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485379</v>
+        <v>485504</v>
       </c>
       <c r="R8" t="n">
-        <v>7085196</v>
+        <v>7085265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132706120</v>
+        <v>132706133</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485504</v>
+        <v>485379</v>
       </c>
       <c r="R9" t="n">
-        <v>7085265</v>
+        <v>7085196</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132706130</v>
+        <v>132706118</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485688</v>
+        <v>485671</v>
       </c>
       <c r="R12" t="n">
-        <v>7085710</v>
+        <v>7085660</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132706118</v>
+        <v>132706130</v>
       </c>
       <c r="B13" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485671</v>
+        <v>485688</v>
       </c>
       <c r="R13" t="n">
-        <v>7085660</v>
+        <v>7085710</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,6 +1833,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,7 +1966,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132706101</v>
+        <v>132706102</v>
       </c>
       <c r="B15" t="n">
         <v>57958</v>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485436</v>
+        <v>485363</v>
       </c>
       <c r="R15" t="n">
-        <v>7085206</v>
+        <v>7085199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132706102</v>
+        <v>132706101</v>
       </c>
       <c r="B16" t="n">
         <v>57958</v>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485363</v>
+        <v>485436</v>
       </c>
       <c r="R16" t="n">
-        <v>7085199</v>
+        <v>7085206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 13529-2026 artfynd.xlsx
+++ b/artfynd/A 13529-2026 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132706119</v>
+        <v>132706122</v>
       </c>
       <c r="B4" t="n">
-        <v>80438</v>
+        <v>91914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485670</v>
+        <v>485491</v>
       </c>
       <c r="R4" t="n">
-        <v>7085635</v>
+        <v>7085550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132706122</v>
+        <v>132706119</v>
       </c>
       <c r="B5" t="n">
-        <v>91914</v>
+        <v>80438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485491</v>
+        <v>485670</v>
       </c>
       <c r="R5" t="n">
-        <v>7085550</v>
+        <v>7085635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132706117</v>
+        <v>132706129</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485449</v>
+        <v>485559</v>
       </c>
       <c r="R6" t="n">
-        <v>7085557</v>
+        <v>7085853</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132706129</v>
+        <v>132706117</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485559</v>
+        <v>485449</v>
       </c>
       <c r="R7" t="n">
-        <v>7085853</v>
+        <v>7085557</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132706120</v>
+        <v>132706133</v>
       </c>
       <c r="B8" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485504</v>
+        <v>485379</v>
       </c>
       <c r="R8" t="n">
-        <v>7085265</v>
+        <v>7085196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132706133</v>
+        <v>132706120</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485379</v>
+        <v>485504</v>
       </c>
       <c r="R9" t="n">
-        <v>7085196</v>
+        <v>7085265</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132706118</v>
+        <v>132706130</v>
       </c>
       <c r="B12" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485671</v>
+        <v>485688</v>
       </c>
       <c r="R12" t="n">
-        <v>7085660</v>
+        <v>7085710</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1736,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,10 +1767,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132706130</v>
+        <v>132706118</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1778,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1802,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485688</v>
+        <v>485671</v>
       </c>
       <c r="R13" t="n">
-        <v>7085710</v>
+        <v>7085660</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1833,11 +1838,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,7 +1966,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132706102</v>
+        <v>132706101</v>
       </c>
       <c r="B15" t="n">
         <v>57958</v>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485363</v>
+        <v>485436</v>
       </c>
       <c r="R15" t="n">
-        <v>7085199</v>
+        <v>7085206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132706101</v>
+        <v>132706102</v>
       </c>
       <c r="B16" t="n">
         <v>57958</v>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485436</v>
+        <v>485363</v>
       </c>
       <c r="R16" t="n">
-        <v>7085206</v>
+        <v>7085199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 13529-2026 artfynd.xlsx
+++ b/artfynd/A 13529-2026 artfynd.xlsx
@@ -1966,7 +1966,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132706101</v>
+        <v>132706102</v>
       </c>
       <c r="B15" t="n">
         <v>57958</v>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485436</v>
+        <v>485363</v>
       </c>
       <c r="R15" t="n">
-        <v>7085206</v>
+        <v>7085199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132706102</v>
+        <v>132706101</v>
       </c>
       <c r="B16" t="n">
         <v>57958</v>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485363</v>
+        <v>485436</v>
       </c>
       <c r="R16" t="n">
-        <v>7085199</v>
+        <v>7085206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 13529-2026 artfynd.xlsx
+++ b/artfynd/A 13529-2026 artfynd.xlsx
@@ -1867,7 +1867,7 @@
         <v>132706100</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132706102</v>
+        <v>132706101</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485363</v>
+        <v>485436</v>
       </c>
       <c r="R15" t="n">
-        <v>7085199</v>
+        <v>7085206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132706101</v>
+        <v>132706102</v>
       </c>
       <c r="B16" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485436</v>
+        <v>485363</v>
       </c>
       <c r="R16" t="n">
-        <v>7085206</v>
+        <v>7085199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 13529-2026 artfynd.xlsx
+++ b/artfynd/A 13529-2026 artfynd.xlsx
@@ -1867,7 +1867,7 @@
         <v>132706100</v>
       </c>
       <c r="B14" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>132706101</v>
       </c>
       <c r="B15" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>132706102</v>
       </c>
       <c r="B16" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 13529-2026 artfynd.xlsx
+++ b/artfynd/A 13529-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132706121</v>
+        <v>132706122</v>
       </c>
       <c r="B2" t="n">
-        <v>80438</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485467</v>
+        <v>485491</v>
       </c>
       <c r="R2" t="n">
-        <v>7085614</v>
+        <v>7085550</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132706132</v>
+        <v>132706127</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485643</v>
+        <v>485429</v>
       </c>
       <c r="R3" t="n">
-        <v>7085608</v>
+        <v>7085548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132706122</v>
+        <v>132706128</v>
       </c>
       <c r="B4" t="n">
-        <v>91914</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485491</v>
+        <v>485650</v>
       </c>
       <c r="R4" t="n">
-        <v>7085550</v>
+        <v>7085736</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132706119</v>
+        <v>132706129</v>
       </c>
       <c r="B5" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485670</v>
+        <v>485559</v>
       </c>
       <c r="R5" t="n">
-        <v>7085635</v>
+        <v>7085853</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,14 +1078,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132706129</v>
+        <v>132706130</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1103,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485559</v>
+        <v>485688</v>
       </c>
       <c r="R6" t="n">
-        <v>7085853</v>
+        <v>7085710</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132706117</v>
+        <v>132706131</v>
       </c>
       <c r="B7" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485449</v>
+        <v>485674</v>
       </c>
       <c r="R7" t="n">
-        <v>7085557</v>
+        <v>7085670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1251,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,14 +1282,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132706133</v>
+        <v>132706132</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1302,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485379</v>
+        <v>485643</v>
       </c>
       <c r="R8" t="n">
-        <v>7085196</v>
+        <v>7085608</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1353,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1384,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132706120</v>
+        <v>132706133</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485504</v>
+        <v>485379</v>
       </c>
       <c r="R9" t="n">
-        <v>7085265</v>
+        <v>7085196</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132706131</v>
+        <v>132706117</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485674</v>
+        <v>485449</v>
       </c>
       <c r="R10" t="n">
-        <v>7085670</v>
+        <v>7085557</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132706128</v>
+        <v>132706118</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>80488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485650</v>
+        <v>485671</v>
       </c>
       <c r="R11" t="n">
-        <v>7085736</v>
+        <v>7085660</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1649,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132706130</v>
+        <v>132706119</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>80488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485688</v>
+        <v>485670</v>
       </c>
       <c r="R12" t="n">
-        <v>7085710</v>
+        <v>7085635</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,11 +1746,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132706118</v>
+        <v>132706120</v>
       </c>
       <c r="B13" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485671</v>
+        <v>485504</v>
       </c>
       <c r="R13" t="n">
-        <v>7085660</v>
+        <v>7085265</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132706100</v>
+        <v>132706121</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1899,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485644</v>
+        <v>485467</v>
       </c>
       <c r="R14" t="n">
-        <v>7085875</v>
+        <v>7085614</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1935,11 +1940,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,7 +1966,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132706101</v>
+        <v>132706100</v>
       </c>
       <c r="B15" t="n">
         <v>57975</v>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485436</v>
+        <v>485644</v>
       </c>
       <c r="R15" t="n">
-        <v>7085206</v>
+        <v>7085875</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2068,7 +2068,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132706102</v>
+        <v>132706101</v>
       </c>
       <c r="B16" t="n">
         <v>57975</v>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485363</v>
+        <v>485436</v>
       </c>
       <c r="R16" t="n">
-        <v>7085199</v>
+        <v>7085206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2167,6 +2167,108 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132706102</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tuvattnet N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>485363</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7085199</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
